--- a/docs/vsscript/VSScript-Manual-Case.xlsx
+++ b/docs/vsscript/VSScript-Manual-Case.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\inetsoft\sr14_0\newtest\datatest\vsscript\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\inetsoft\stylebi\test\datatest\docs\vsscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="OverView" sheetId="3" r:id="rId1"/>
@@ -167,9 +167,6 @@
     <t>open viewsheet properties and modify the script email address to a valid address(below red rectangle), then save the vs</t>
   </si>
   <si>
-    <t>new a task name with 'schTask1', and select the vs</t>
-  </si>
-  <si>
     <t>input another emails address, then run the task</t>
   </si>
   <si>
@@ -359,9 +356,6 @@
     <t>3. Freehand title show right condition</t>
   </si>
   <si>
-    <t>TestCase-hyperlink</t>
-  </si>
-  <si>
     <t>Test Viewsheet setHyperlink script</t>
   </si>
   <si>
@@ -428,9 +422,6 @@
     <t>Test Viewsheet table,crosstab,freehand ActionVisible script</t>
   </si>
   <si>
-    <t>TestCase-ActionVisible</t>
-  </si>
-  <si>
     <t>Test Selection action visible script</t>
   </si>
   <si>
@@ -719,9 +710,6 @@
     <t>the Text show right info</t>
   </si>
   <si>
-    <t>TestCase- SubmitOnClick</t>
-  </si>
-  <si>
     <t>Test all form assemblies SubmitOnClick script</t>
   </si>
   <si>
@@ -1289,16 +1277,7 @@
     <t>TestCase-pviewsheet</t>
   </si>
   <si>
-    <t>Test pviewsheet script usage</t>
-  </si>
-  <si>
     <t>on portal side, open Manual/OtherScript/pViewsheet</t>
-  </si>
-  <si>
-    <t>select 'Link to VS' text</t>
-  </si>
-  <si>
-    <t>The VS Text value should show as:</t>
   </si>
   <si>
     <t>TestCase-saveworksheet</t>
@@ -1352,14 +1331,6 @@
   </si>
   <si>
     <t xml:space="preserve">                             </t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>Setting "graph.script.action.support = true"in sree.properties dialog</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>Click ok button,and save this viewsheet named "graphaction"</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
@@ -1428,14 +1399,6 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>open http://localhost:8080/sree/export/viewsheet/global/Manual/OtherScript/scopePara4?outtype=PNG&amp;myPara=testbbb</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>open 'http://localhost:8090/sree/app/viewer/view/global/Manual/OtherScript/scopePara4?myPara=testaaa'</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
     <t>Test Event script usage</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
@@ -1444,10 +1407,6 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>TestCase-scriptAction</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
     <t>Preview this viewsheet,click Image</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
@@ -1487,10 +1446,6 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>TestCase-TextActions</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
     <t>TestCase-parameterScript</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
@@ -1500,10 +1455,6 @@
   </si>
   <si>
     <t>on portal side, open Manual/OtherScript/Script_Order_OneWay4</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>In parameter dialog, input 'NK,NY,NJ', click ok button</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
@@ -2039,6 +1990,62 @@
     <t>1. open linked_vs</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
+  <si>
+    <t>new a task name with 'schTask1', and select the vs</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>open 'http://localhost:8090/sree/app/viewer/view/global/Manual/OtherScript/scopePara4?myPara=testaaa'</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>open http://localhost:8080/sree/export/viewsheet/global/Manual/OtherScript/scopePara4?outtype=PNG&amp;myPara=testbbb</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Test pviewsheet script usage</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>select 'Link to VS' text</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>The VS Text value should show as:</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>In parameter dialog, input 'NK,NY,NJ', click ok button</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Click ok button,and save this viewsheet named "graphaction"</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>TestCase-scriptAction</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Setting "graph.script.action.support = true"in sree.properties dialog</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>TestCase-hyperlink</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>TestCase-ActionVisible</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>TestCase- SubmitOnClick</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>TestCase-TextActions</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2178,7 +2185,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2212,6 +2219,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2409,7 +2422,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1">
@@ -2504,12 +2517,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2583,6 +2590,30 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="2" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="2" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -6556,27 +6587,27 @@
       </c>
     </row>
     <row r="13" spans="2:5">
-      <c r="E13" s="38" t="s">
+      <c r="E13" s="36" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="42">
+      <c r="C14" s="38"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="40">
         <v>32</v>
       </c>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="39" t="s">
+      <c r="B15" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="42">
+      <c r="C15" s="38"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="40">
         <v>22</v>
       </c>
     </row>
@@ -6797,10 +6828,10 @@
       <c r="E22" s="16"/>
       <c r="F22" s="16"/>
       <c r="G22" s="16"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
     </row>
     <row r="23" spans="1:11">
       <c r="B23" s="18" t="s">
@@ -6809,10 +6840,10 @@
       <c r="C23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="43"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41"/>
+      <c r="J23" s="41"/>
+      <c r="K23" s="41"/>
     </row>
     <row r="27" spans="1:11">
       <c r="C27" s="2" t="s">
@@ -6930,13 +6961,13 @@
     </row>
     <row r="43" spans="1:9">
       <c r="C43" s="2" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
     </row>
     <row r="51" spans="1:3">
@@ -7041,7 +7072,7 @@
     </row>
     <row r="65" spans="1:9">
       <c r="C65" s="2" t="s">
-        <v>476</v>
+        <v>462</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -7175,7 +7206,7 @@
         <v>3</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>48</v>
+        <v>537</v>
       </c>
     </row>
     <row r="91" spans="1:3">
@@ -7183,7 +7214,7 @@
         <v>4</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="92" spans="1:3">
@@ -7191,17 +7222,17 @@
         <v>23</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="1:3">
       <c r="C93" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="94" spans="1:3">
       <c r="C94" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="95" spans="1:3">
@@ -7209,7 +7240,7 @@
         <v>5</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="96" spans="1:3">
@@ -7217,7 +7248,7 @@
         <v>6</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="97" spans="1:10">
@@ -7225,17 +7256,17 @@
         <v>23</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98" spans="1:10">
       <c r="C98" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="99" spans="1:10">
       <c r="C99" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="100" spans="1:10">
@@ -7243,7 +7274,7 @@
         <v>7</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101" spans="1:10">
@@ -7251,7 +7282,7 @@
         <v>8</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="102" spans="1:10">
@@ -7259,27 +7290,27 @@
         <v>23</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
     </row>
     <row r="103" spans="1:10">
-      <c r="C103" s="45" t="s">
+      <c r="C103" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="D103" s="43"/>
+      <c r="E103" s="43"/>
+      <c r="F103" s="43"/>
+      <c r="G103" s="44" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="104" spans="1:10">
+      <c r="C104" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="D103" s="45"/>
-      <c r="E103" s="45"/>
-      <c r="F103" s="45"/>
-      <c r="G103" s="46" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="104" spans="1:10">
-      <c r="C104" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="D104" s="45"/>
-      <c r="E104" s="45"/>
-      <c r="F104" s="45"/>
+      <c r="D104" s="43"/>
+      <c r="E104" s="43"/>
+      <c r="F104" s="43"/>
     </row>
     <row r="106" spans="1:10">
       <c r="A106" s="10"/>
@@ -7300,7 +7331,7 @@
     </row>
     <row r="109" spans="1:10">
       <c r="A109" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B109" s="13"/>
       <c r="C109" s="13"/>
@@ -7326,7 +7357,7 @@
     <row r="111" spans="1:10">
       <c r="A111" s="15"/>
       <c r="B111" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C111" s="15"/>
       <c r="D111" s="15"/>
@@ -7374,7 +7405,7 @@
         <v>1</v>
       </c>
       <c r="B115" s="16" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C115" s="16"/>
       <c r="D115" s="16"/>
@@ -7388,7 +7419,7 @@
         <v>2</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -7396,12 +7427,12 @@
         <v>23</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="134" spans="1:9">
       <c r="A134" s="12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B134" s="13"/>
       <c r="C134" s="13"/>
@@ -7427,7 +7458,7 @@
     <row r="136" spans="1:9">
       <c r="A136" s="15"/>
       <c r="B136" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C136" s="15"/>
       <c r="D136" s="15"/>
@@ -7475,7 +7506,7 @@
         <v>1</v>
       </c>
       <c r="B140" s="16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C140" s="16"/>
       <c r="D140" s="16"/>
@@ -7489,7 +7520,7 @@
         <v>2</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="142" spans="1:9">
@@ -7497,12 +7528,12 @@
         <v>23</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="174" spans="1:9">
       <c r="A174" s="12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B174" s="13"/>
       <c r="C174" s="13"/>
@@ -7528,7 +7559,7 @@
     <row r="176" spans="1:9">
       <c r="A176" s="15"/>
       <c r="B176" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C176" s="15"/>
       <c r="D176" s="15"/>
@@ -7576,7 +7607,7 @@
         <v>1</v>
       </c>
       <c r="B180" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C180" s="16"/>
       <c r="D180" s="16"/>
@@ -7590,7 +7621,7 @@
         <v>2</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -7598,12 +7629,12 @@
         <v>23</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="202" spans="1:9">
       <c r="A202" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B202" s="13"/>
       <c r="C202" s="13"/>
@@ -7627,7 +7658,7 @@
     <row r="204" spans="1:9">
       <c r="A204" s="15"/>
       <c r="B204" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C204" s="15"/>
       <c r="D204" s="15"/>
@@ -7667,7 +7698,7 @@
         <v>1</v>
       </c>
       <c r="B208" s="16" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C208" s="16"/>
       <c r="D208" s="16"/>
@@ -7679,7 +7710,7 @@
         <v>2</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -7687,12 +7718,12 @@
         <v>23</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="241" spans="1:9">
       <c r="A241" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B241" s="13"/>
       <c r="C241" s="13"/>
@@ -7716,7 +7747,7 @@
     <row r="243" spans="1:9">
       <c r="A243" s="15"/>
       <c r="B243" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C243" s="15"/>
       <c r="D243" s="15"/>
@@ -7756,7 +7787,7 @@
         <v>1</v>
       </c>
       <c r="B247" s="16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C247" s="16"/>
       <c r="D247" s="16"/>
@@ -7768,7 +7799,7 @@
         <v>2</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="249" spans="1:9">
@@ -7776,12 +7807,12 @@
         <v>23</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="254" spans="1:9">
       <c r="A254" s="12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B254" s="13"/>
       <c r="C254" s="13"/>
@@ -7805,7 +7836,7 @@
     <row r="256" spans="1:9">
       <c r="A256" s="15"/>
       <c r="B256" s="15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C256" s="15"/>
       <c r="D256" s="15"/>
@@ -7845,7 +7876,7 @@
         <v>1</v>
       </c>
       <c r="B260" s="16" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C260" s="16"/>
       <c r="D260" s="16"/>
@@ -7857,7 +7888,7 @@
         <v>2</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="262" spans="1:6">
@@ -7865,12 +7896,12 @@
         <v>23</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="281" spans="1:9">
       <c r="A281" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B281" s="13"/>
       <c r="C281" s="13"/>
@@ -7894,7 +7925,7 @@
     <row r="283" spans="1:9">
       <c r="A283" s="15"/>
       <c r="B283" s="15" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C283" s="15"/>
       <c r="D283" s="15"/>
@@ -7934,7 +7965,7 @@
         <v>1</v>
       </c>
       <c r="B287" s="16" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C287" s="16"/>
       <c r="D287" s="16"/>
@@ -7943,10 +7974,10 @@
     </row>
     <row r="288" spans="1:9">
       <c r="B288" s="18" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
     </row>
     <row r="289" spans="1:9">
@@ -7954,7 +7985,7 @@
         <v>2</v>
       </c>
       <c r="B289" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="290" spans="1:9">
@@ -7962,12 +7993,12 @@
         <v>23</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
     </row>
     <row r="292" spans="1:9">
       <c r="A292" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B292" s="13"/>
       <c r="C292" s="13"/>
@@ -7991,7 +8022,7 @@
     <row r="294" spans="1:9">
       <c r="A294" s="15"/>
       <c r="B294" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C294" s="15"/>
       <c r="D294" s="15"/>
@@ -8031,7 +8062,7 @@
         <v>1</v>
       </c>
       <c r="B298" s="16" t="s">
-        <v>514</v>
+        <v>500</v>
       </c>
       <c r="C298" s="16"/>
       <c r="D298" s="16"/>
@@ -8043,7 +8074,7 @@
         <v>2</v>
       </c>
       <c r="B299" s="16" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="300" spans="1:9">
@@ -8051,12 +8082,12 @@
         <v>23</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="318" spans="1:9">
       <c r="A318" s="12" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B318" s="13"/>
       <c r="C318" s="13"/>
@@ -8080,7 +8111,7 @@
     <row r="320" spans="1:9">
       <c r="A320" s="15"/>
       <c r="B320" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C320" s="15"/>
       <c r="D320" s="15"/>
@@ -8120,7 +8151,7 @@
         <v>1</v>
       </c>
       <c r="B324" s="16" t="s">
-        <v>515</v>
+        <v>501</v>
       </c>
       <c r="C324" s="16"/>
       <c r="D324" s="16"/>
@@ -8132,7 +8163,7 @@
         <v>2</v>
       </c>
       <c r="B325" s="16" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -8140,12 +8171,12 @@
         <v>23</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="350" spans="1:9">
       <c r="A350" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B350" s="13"/>
       <c r="C350" s="13"/>
@@ -8169,7 +8200,7 @@
     <row r="352" spans="1:9">
       <c r="A352" s="15"/>
       <c r="B352" s="15" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C352" s="15"/>
       <c r="D352" s="15"/>
@@ -8209,7 +8240,7 @@
         <v>1</v>
       </c>
       <c r="B356" s="16" t="s">
-        <v>516</v>
+        <v>502</v>
       </c>
       <c r="C356" s="16"/>
       <c r="D356" s="16"/>
@@ -8221,7 +8252,7 @@
         <v>2</v>
       </c>
       <c r="B357" s="16" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="358" spans="1:6">
@@ -8229,12 +8260,12 @@
         <v>23</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="359" spans="1:6">
       <c r="C359" s="2" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
     </row>
     <row r="360" spans="1:6">
@@ -8242,7 +8273,7 @@
         <v>3</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="361" spans="1:6">
@@ -8250,7 +8281,7 @@
         <v>23</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="378" spans="1:9" s="10" customFormat="1" ht="5.25" customHeight="1"/>
@@ -8261,7 +8292,7 @@
     </row>
     <row r="381" spans="1:9">
       <c r="A381" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B381" s="13"/>
       <c r="C381" s="13"/>
@@ -8288,7 +8319,7 @@
     <row r="383" spans="1:9">
       <c r="A383" s="15"/>
       <c r="B383" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C383" s="15"/>
       <c r="D383" s="15"/>
@@ -8340,7 +8371,7 @@
         <v>1</v>
       </c>
       <c r="B387" s="16" t="s">
-        <v>517</v>
+        <v>503</v>
       </c>
       <c r="C387" s="16"/>
       <c r="D387" s="16"/>
@@ -8355,7 +8386,7 @@
         <v>2</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="389" spans="1:9">
@@ -8363,12 +8394,12 @@
         <v>23</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="390" spans="1:9">
       <c r="C390" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="401" spans="1:3">
@@ -8376,7 +8407,7 @@
         <v>3</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="402" spans="1:3">
@@ -8384,12 +8415,12 @@
         <v>23</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="403" spans="1:3">
       <c r="C403" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="415" spans="1:3">
@@ -8397,7 +8428,7 @@
         <v>4</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="416" spans="1:3">
@@ -8405,17 +8436,17 @@
         <v>23</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="417" spans="1:9">
       <c r="C417" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="430" spans="1:9">
       <c r="A430" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B430" s="13"/>
       <c r="C430" s="13"/>
@@ -8442,7 +8473,7 @@
     <row r="432" spans="1:9">
       <c r="A432" s="15"/>
       <c r="B432" s="15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C432" s="15"/>
       <c r="D432" s="15"/>
@@ -8494,7 +8525,7 @@
         <v>1</v>
       </c>
       <c r="B436" s="16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C436" s="16"/>
       <c r="D436" s="16"/>
@@ -8509,7 +8540,7 @@
         <v>2</v>
       </c>
       <c r="B437" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="438" spans="1:9">
@@ -8517,22 +8548,22 @@
         <v>23</v>
       </c>
       <c r="C438" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="439" spans="1:9">
       <c r="C439" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="440" spans="1:9">
       <c r="C440" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="458" spans="1:9">
       <c r="A458" s="12" t="s">
-        <v>112</v>
+        <v>547</v>
       </c>
       <c r="B458" s="13"/>
       <c r="C458" s="13"/>
@@ -8559,7 +8590,7 @@
     <row r="460" spans="1:9">
       <c r="A460" s="15"/>
       <c r="B460" s="15" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C460" s="15"/>
       <c r="D460" s="15"/>
@@ -8611,7 +8642,7 @@
         <v>1</v>
       </c>
       <c r="B464" s="16" t="s">
-        <v>518</v>
+        <v>504</v>
       </c>
       <c r="C464" s="16"/>
       <c r="D464" s="16"/>
@@ -8626,7 +8657,7 @@
         <v>2</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="466" spans="1:3">
@@ -8634,7 +8665,7 @@
         <v>23</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="472" spans="1:3">
@@ -8642,7 +8673,7 @@
         <v>3</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="473" spans="1:3">
@@ -8650,7 +8681,7 @@
         <v>23</v>
       </c>
       <c r="C473" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="474" spans="1:3">
@@ -8658,7 +8689,7 @@
         <v>4</v>
       </c>
       <c r="B474" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="475" spans="1:3">
@@ -8666,7 +8697,7 @@
         <v>23</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="476" spans="1:3">
@@ -8674,7 +8705,7 @@
         <v>5</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="482" spans="1:3">
@@ -8682,12 +8713,12 @@
         <v>23</v>
       </c>
       <c r="C482" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="483" spans="1:3">
       <c r="C483" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="484" spans="1:3">
@@ -8695,7 +8726,7 @@
         <v>6</v>
       </c>
       <c r="B484" s="2" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
     </row>
     <row r="489" spans="1:3">
@@ -8703,17 +8734,17 @@
         <v>23</v>
       </c>
       <c r="C489" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="490" spans="1:3">
       <c r="C490" s="2" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
     </row>
     <row r="497" spans="1:9">
       <c r="A497" s="12" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B497" s="13"/>
       <c r="C497" s="13"/>
@@ -8740,7 +8771,7 @@
     <row r="499" spans="1:9">
       <c r="A499" s="15"/>
       <c r="B499" s="15" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C499" s="15"/>
       <c r="D499" s="15"/>
@@ -8766,7 +8797,7 @@
     <row r="501" spans="1:9">
       <c r="A501" s="14"/>
       <c r="B501" s="17" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C501" s="17"/>
       <c r="D501" s="15"/>
@@ -8794,7 +8825,7 @@
         <v>1</v>
       </c>
       <c r="B503" s="16" t="s">
-        <v>519</v>
+        <v>505</v>
       </c>
       <c r="C503" s="16"/>
       <c r="D503" s="16"/>
@@ -8809,7 +8840,7 @@
         <v>23</v>
       </c>
       <c r="C504" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="505" spans="1:9">
@@ -8817,7 +8848,7 @@
         <v>2</v>
       </c>
       <c r="B505" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="506" spans="1:9">
@@ -8825,12 +8856,12 @@
         <v>23</v>
       </c>
       <c r="C506" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="512" spans="1:9">
       <c r="C512" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="513" spans="1:9">
@@ -8838,7 +8869,7 @@
         <v>3</v>
       </c>
       <c r="B513" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="514" spans="1:9">
@@ -8846,17 +8877,17 @@
         <v>23</v>
       </c>
       <c r="C514" s="2" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
     </row>
     <row r="515" spans="1:9">
       <c r="C515" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="520" spans="1:9">
       <c r="A520" s="12" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B520" s="13"/>
       <c r="C520" s="13"/>
@@ -8883,7 +8914,7 @@
     <row r="522" spans="1:9">
       <c r="A522" s="15"/>
       <c r="B522" s="15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C522" s="15"/>
       <c r="D522" s="15"/>
@@ -8935,7 +8966,7 @@
         <v>1</v>
       </c>
       <c r="B526" s="16" t="s">
-        <v>520</v>
+        <v>506</v>
       </c>
       <c r="C526" s="16"/>
       <c r="D526" s="16"/>
@@ -8950,7 +8981,7 @@
         <v>2</v>
       </c>
       <c r="B527" s="16" t="s">
-        <v>521</v>
+        <v>507</v>
       </c>
       <c r="C527" s="16"/>
       <c r="D527" s="16"/>
@@ -8964,117 +8995,117 @@
       <c r="A528" s="16"/>
       <c r="B528" s="16"/>
       <c r="D528" s="16"/>
-      <c r="F528" s="53" t="s">
-        <v>532</v>
-      </c>
-      <c r="G528" s="54"/>
-      <c r="H528" s="54"/>
-      <c r="I528" s="55"/>
+      <c r="F528" s="51" t="s">
+        <v>518</v>
+      </c>
+      <c r="G528" s="52"/>
+      <c r="H528" s="52"/>
+      <c r="I528" s="53"/>
     </row>
     <row r="529" spans="1:9">
       <c r="A529" s="16"/>
-      <c r="B529" s="47" t="s">
-        <v>522</v>
-      </c>
-      <c r="C529" s="50" t="s">
-        <v>524</v>
-      </c>
-      <c r="D529" s="51"/>
-      <c r="E529" s="52"/>
-      <c r="F529" s="56" t="s">
-        <v>527</v>
-      </c>
-      <c r="G529" s="57"/>
-      <c r="H529" s="57"/>
+      <c r="B529" s="45" t="s">
+        <v>508</v>
+      </c>
+      <c r="C529" s="48" t="s">
+        <v>510</v>
+      </c>
+      <c r="D529" s="49"/>
+      <c r="E529" s="50"/>
+      <c r="F529" s="54" t="s">
+        <v>513</v>
+      </c>
+      <c r="G529" s="55"/>
+      <c r="H529" s="55"/>
       <c r="I529" s="32"/>
     </row>
     <row r="530" spans="1:9">
       <c r="A530" s="16"/>
-      <c r="B530" s="48"/>
-      <c r="C530" s="50" t="s">
-        <v>523</v>
-      </c>
-      <c r="D530" s="51"/>
-      <c r="E530" s="52"/>
+      <c r="B530" s="46"/>
+      <c r="C530" s="48" t="s">
+        <v>509</v>
+      </c>
+      <c r="D530" s="49"/>
+      <c r="E530" s="50"/>
       <c r="F530" s="35"/>
-      <c r="G530" s="58"/>
-      <c r="H530" s="58"/>
-      <c r="I530" s="59"/>
+      <c r="G530" s="56"/>
+      <c r="H530" s="56"/>
+      <c r="I530" s="57"/>
     </row>
     <row r="531" spans="1:9">
       <c r="A531" s="16"/>
-      <c r="B531" s="47" t="s">
-        <v>525</v>
-      </c>
-      <c r="C531" s="50" t="s">
-        <v>526</v>
-      </c>
-      <c r="D531" s="51"/>
-      <c r="E531" s="52"/>
-      <c r="F531" s="56" t="s">
-        <v>527</v>
-      </c>
-      <c r="G531" s="57"/>
-      <c r="H531" s="57"/>
-      <c r="I531" s="60"/>
+      <c r="B531" s="45" t="s">
+        <v>511</v>
+      </c>
+      <c r="C531" s="48" t="s">
+        <v>512</v>
+      </c>
+      <c r="D531" s="49"/>
+      <c r="E531" s="50"/>
+      <c r="F531" s="54" t="s">
+        <v>513</v>
+      </c>
+      <c r="G531" s="55"/>
+      <c r="H531" s="55"/>
+      <c r="I531" s="58"/>
     </row>
     <row r="532" spans="1:9">
       <c r="A532" s="16"/>
-      <c r="B532" s="49"/>
-      <c r="C532" s="50" t="s">
-        <v>531</v>
-      </c>
-      <c r="D532" s="51"/>
-      <c r="E532" s="52"/>
+      <c r="B532" s="47"/>
+      <c r="C532" s="48" t="s">
+        <v>517</v>
+      </c>
+      <c r="D532" s="49"/>
+      <c r="E532" s="50"/>
       <c r="F532" s="19"/>
-      <c r="G532" s="61"/>
-      <c r="H532" s="61"/>
-      <c r="I532" s="62"/>
+      <c r="G532" s="59"/>
+      <c r="H532" s="59"/>
+      <c r="I532" s="60"/>
     </row>
     <row r="533" spans="1:9">
       <c r="A533" s="16"/>
       <c r="B533" s="29"/>
-      <c r="C533" s="50" t="s">
-        <v>533</v>
-      </c>
-      <c r="D533" s="51"/>
-      <c r="E533" s="52"/>
-      <c r="F533" s="63" t="s">
-        <v>530</v>
-      </c>
-      <c r="G533" s="58"/>
-      <c r="H533" s="58"/>
-      <c r="I533" s="59"/>
+      <c r="C533" s="48" t="s">
+        <v>519</v>
+      </c>
+      <c r="D533" s="49"/>
+      <c r="E533" s="50"/>
+      <c r="F533" s="61" t="s">
+        <v>516</v>
+      </c>
+      <c r="G533" s="56"/>
+      <c r="H533" s="56"/>
+      <c r="I533" s="57"/>
     </row>
     <row r="534" spans="1:9">
       <c r="A534" s="16"/>
       <c r="B534" s="28" t="s">
-        <v>528</v>
-      </c>
-      <c r="C534" s="50" t="s">
-        <v>529</v>
-      </c>
-      <c r="D534" s="51"/>
-      <c r="E534" s="52"/>
-      <c r="F534" s="56" t="s">
-        <v>527</v>
-      </c>
-      <c r="G534" s="57"/>
-      <c r="H534" s="57"/>
-      <c r="I534" s="60"/>
+        <v>514</v>
+      </c>
+      <c r="C534" s="48" t="s">
+        <v>515</v>
+      </c>
+      <c r="D534" s="49"/>
+      <c r="E534" s="50"/>
+      <c r="F534" s="54" t="s">
+        <v>513</v>
+      </c>
+      <c r="G534" s="55"/>
+      <c r="H534" s="55"/>
+      <c r="I534" s="58"/>
     </row>
     <row r="535" spans="1:9">
       <c r="A535" s="16"/>
-      <c r="B535" s="48"/>
-      <c r="C535" s="50" t="s">
-        <v>531</v>
-      </c>
-      <c r="D535" s="51"/>
-      <c r="E535" s="52"/>
-      <c r="F535" s="63"/>
-      <c r="G535" s="58"/>
-      <c r="H535" s="58"/>
-      <c r="I535" s="59"/>
+      <c r="B535" s="46"/>
+      <c r="C535" s="48" t="s">
+        <v>517</v>
+      </c>
+      <c r="D535" s="49"/>
+      <c r="E535" s="50"/>
+      <c r="F535" s="61"/>
+      <c r="G535" s="56"/>
+      <c r="H535" s="56"/>
+      <c r="I535" s="57"/>
     </row>
     <row r="536" spans="1:9">
       <c r="A536" s="16"/>
@@ -9113,7 +9144,7 @@
     </row>
     <row r="540" spans="1:9">
       <c r="A540" s="12" t="s">
-        <v>135</v>
+        <v>548</v>
       </c>
       <c r="B540" s="13"/>
       <c r="C540" s="13"/>
@@ -9136,7 +9167,7 @@
     <row r="542" spans="1:9">
       <c r="A542" s="15"/>
       <c r="B542" s="15" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C542" s="15"/>
       <c r="D542" s="15"/>
@@ -9172,7 +9203,7 @@
         <v>1</v>
       </c>
       <c r="B546" s="16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C546" s="16"/>
       <c r="D546" s="16"/>
@@ -9183,7 +9214,7 @@
         <v>2</v>
       </c>
       <c r="B547" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="548" spans="1:5">
@@ -9199,7 +9230,7 @@
         <v>3</v>
       </c>
       <c r="B553" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="554" spans="1:5">
@@ -9212,7 +9243,7 @@
         <v>4</v>
       </c>
       <c r="B561" s="2" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="562" spans="1:9">
@@ -9220,7 +9251,7 @@
         <v>23</v>
       </c>
       <c r="C562" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="570" spans="1:9">
@@ -9228,7 +9259,7 @@
         <v>5</v>
       </c>
       <c r="B570" s="16" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
     </row>
     <row r="571" spans="1:9">
@@ -9236,7 +9267,7 @@
         <v>6</v>
       </c>
       <c r="B571" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="572" spans="1:9">
@@ -9244,12 +9275,12 @@
         <v>23</v>
       </c>
       <c r="C572" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="574" spans="1:9">
       <c r="A574" s="12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B574" s="13"/>
       <c r="C574" s="13"/>
@@ -9276,7 +9307,7 @@
     <row r="576" spans="1:9">
       <c r="A576" s="15"/>
       <c r="B576" s="15" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C576" s="15"/>
       <c r="D576" s="15"/>
@@ -9302,7 +9333,7 @@
     <row r="578" spans="1:10">
       <c r="A578" s="14"/>
       <c r="B578" s="17" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C578" s="17"/>
       <c r="D578" s="15"/>
@@ -9330,7 +9361,7 @@
         <v>1</v>
       </c>
       <c r="B580" s="16" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C580" s="16"/>
       <c r="D580" s="16"/>
@@ -9346,7 +9377,7 @@
         <v>23</v>
       </c>
       <c r="C581" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D581" s="16"/>
       <c r="E581" s="16"/>
@@ -9360,7 +9391,7 @@
         <v>2</v>
       </c>
       <c r="B582" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="583" spans="1:10">
@@ -9368,7 +9399,7 @@
         <v>23</v>
       </c>
       <c r="C583" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="589" spans="1:10">
@@ -9376,7 +9407,7 @@
         <v>3</v>
       </c>
       <c r="B589" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="590" spans="1:10">
@@ -9384,10 +9415,10 @@
         <v>23</v>
       </c>
       <c r="C590" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="J590" s="43" t="s">
-        <v>465</v>
+        <v>147</v>
+      </c>
+      <c r="J590" s="41" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="591" spans="1:10">
@@ -9398,8 +9429,8 @@
     </row>
     <row r="593" spans="1:10">
       <c r="B593" s="18"/>
-      <c r="J593" s="44" t="s">
-        <v>466</v>
+      <c r="J593" s="42" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="594" spans="1:10">
@@ -9419,7 +9450,7 @@
         <v>4</v>
       </c>
       <c r="B598" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="599" spans="1:10">
@@ -9427,12 +9458,12 @@
         <v>23</v>
       </c>
       <c r="C599" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="600" spans="1:10">
       <c r="C600" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="601" spans="1:10">
@@ -9440,7 +9471,7 @@
         <v>5</v>
       </c>
       <c r="B601" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="602" spans="1:10">
@@ -9448,12 +9479,12 @@
         <v>23</v>
       </c>
       <c r="C602" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="609" spans="1:9">
       <c r="A609" s="12" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B609" s="13"/>
       <c r="C609" s="13"/>
@@ -9476,7 +9507,7 @@
     <row r="611" spans="1:9">
       <c r="A611" s="15"/>
       <c r="B611" s="15" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C611" s="15"/>
       <c r="D611" s="15"/>
@@ -9494,7 +9525,7 @@
     <row r="613" spans="1:9">
       <c r="A613" s="14"/>
       <c r="B613" s="17" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C613" s="17"/>
       <c r="D613" s="15"/>
@@ -9514,7 +9545,7 @@
         <v>1</v>
       </c>
       <c r="B615" s="16" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C615" s="16"/>
       <c r="D615" s="16"/>
@@ -9525,7 +9556,7 @@
         <v>2</v>
       </c>
       <c r="B616" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="617" spans="1:9">
@@ -9533,7 +9564,7 @@
         <v>3</v>
       </c>
       <c r="B617" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="618" spans="1:9">
@@ -9541,7 +9572,7 @@
         <v>23</v>
       </c>
       <c r="C618" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="621" spans="1:9">
@@ -9549,7 +9580,7 @@
         <v>4</v>
       </c>
       <c r="B621" s="2" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="622" spans="1:9">
@@ -9557,7 +9588,7 @@
         <v>23</v>
       </c>
       <c r="C622" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="623" spans="1:9">
@@ -9565,7 +9596,7 @@
         <v>5</v>
       </c>
       <c r="B623" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="624" spans="1:9">
@@ -9573,7 +9604,7 @@
         <v>23</v>
       </c>
       <c r="C624" s="2" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="625" spans="1:9">
@@ -9581,7 +9612,7 @@
         <v>6</v>
       </c>
       <c r="B625" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="626" spans="1:9">
@@ -9589,7 +9620,7 @@
         <v>7</v>
       </c>
       <c r="B626" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="627" spans="1:9">
@@ -9597,7 +9628,7 @@
         <v>23</v>
       </c>
       <c r="C627" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="630" spans="1:9">
@@ -9605,7 +9636,7 @@
         <v>8</v>
       </c>
       <c r="B630" s="2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="631" spans="1:9">
@@ -9613,7 +9644,7 @@
         <v>23</v>
       </c>
       <c r="C631" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="632" spans="1:9">
@@ -9621,7 +9652,7 @@
         <v>9</v>
       </c>
       <c r="B632" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="633" spans="1:9">
@@ -9629,12 +9660,12 @@
         <v>23</v>
       </c>
       <c r="C633" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="635" spans="1:9">
       <c r="A635" s="12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B635" s="13"/>
       <c r="C635" s="13"/>
@@ -9657,7 +9688,7 @@
     <row r="637" spans="1:9">
       <c r="A637" s="15"/>
       <c r="B637" s="15" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C637" s="15"/>
       <c r="D637" s="15"/>
@@ -9675,7 +9706,7 @@
     <row r="639" spans="1:9">
       <c r="A639" s="14"/>
       <c r="B639" s="17" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C639" s="17"/>
       <c r="D639" s="15"/>
@@ -9695,7 +9726,7 @@
         <v>1</v>
       </c>
       <c r="B641" s="16" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C641" s="16"/>
       <c r="D641" s="16"/>
@@ -9706,12 +9737,12 @@
         <v>2</v>
       </c>
       <c r="B642" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="643" spans="1:8">
       <c r="B643" s="3" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C643" s="26"/>
       <c r="D643" s="27" t="s">
@@ -9724,13 +9755,13 @@
     </row>
     <row r="644" spans="1:8">
       <c r="B644" s="28" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C644" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D644" s="7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E644" s="8"/>
       <c r="F644" s="8"/>
@@ -9743,7 +9774,7 @@
         <v>1</v>
       </c>
       <c r="D645" s="7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E645" s="8"/>
       <c r="F645" s="8"/>
@@ -9752,13 +9783,13 @@
     </row>
     <row r="646" spans="1:8">
       <c r="B646" s="28" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C646" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D646" s="7" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E646" s="8"/>
       <c r="F646" s="8"/>
@@ -9771,7 +9802,7 @@
         <v>1</v>
       </c>
       <c r="D647" s="7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E647" s="8"/>
       <c r="F647" s="8"/>
@@ -9780,13 +9811,13 @@
     </row>
     <row r="648" spans="1:8">
       <c r="B648" s="28" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C648" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D648" s="7" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E648" s="8"/>
       <c r="F648" s="8"/>
@@ -9799,7 +9830,7 @@
         <v>1</v>
       </c>
       <c r="D649" s="7" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E649" s="8"/>
       <c r="F649" s="8"/>
@@ -9808,13 +9839,13 @@
     </row>
     <row r="650" spans="1:8">
       <c r="B650" s="29" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C650" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D650" s="7" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E650" s="8"/>
       <c r="F650" s="8"/>
@@ -9827,7 +9858,7 @@
         <v>1</v>
       </c>
       <c r="D651" s="7" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E651" s="8"/>
       <c r="F651" s="8"/>
@@ -9836,13 +9867,13 @@
     </row>
     <row r="652" spans="1:8">
       <c r="B652" s="28" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C652" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D652" s="7" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E652" s="8"/>
       <c r="F652" s="8"/>
@@ -9855,7 +9886,7 @@
         <v>1</v>
       </c>
       <c r="D653" s="7" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E653" s="8"/>
       <c r="F653" s="8"/>
@@ -9864,13 +9895,13 @@
     </row>
     <row r="654" spans="1:8">
       <c r="B654" s="28" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C654" s="9" t="b">
         <v>0</v>
       </c>
       <c r="D654" s="7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E654" s="8"/>
       <c r="F654" s="8"/>
@@ -9883,7 +9914,7 @@
         <v>1</v>
       </c>
       <c r="D655" s="7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E655" s="8"/>
       <c r="F655" s="8"/>
@@ -9892,7 +9923,7 @@
     </row>
     <row r="656" spans="1:8">
       <c r="B656" s="28" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C656" s="28" t="b">
         <v>0</v>
@@ -9911,24 +9942,27 @@
     </row>
     <row r="658" spans="1:9">
       <c r="B658" s="33"/>
-      <c r="C658" s="28" t="b">
+      <c r="C658" s="65" t="b">
         <v>1</v>
       </c>
-      <c r="D658" s="19"/>
-      <c r="H658" s="34"/>
+      <c r="D658" s="66"/>
+      <c r="E658" s="67"/>
+      <c r="F658" s="67"/>
+      <c r="G658" s="67"/>
+      <c r="H658" s="68"/>
     </row>
     <row r="659" spans="1:9">
       <c r="B659" s="29"/>
-      <c r="C659" s="29"/>
-      <c r="D659" s="35"/>
-      <c r="E659" s="36"/>
-      <c r="F659" s="36"/>
-      <c r="G659" s="36"/>
-      <c r="H659" s="37"/>
+      <c r="C659" s="69"/>
+      <c r="D659" s="70"/>
+      <c r="E659" s="71"/>
+      <c r="F659" s="71"/>
+      <c r="G659" s="71"/>
+      <c r="H659" s="72"/>
     </row>
     <row r="662" spans="1:9">
       <c r="A662" s="12" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B662" s="13"/>
       <c r="C662" s="13"/>
@@ -9951,7 +9985,7 @@
     <row r="664" spans="1:9">
       <c r="A664" s="15"/>
       <c r="B664" s="15" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C664" s="15"/>
       <c r="D664" s="15"/>
@@ -9987,7 +10021,7 @@
         <v>1</v>
       </c>
       <c r="B668" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C668" s="16"/>
       <c r="D668" s="16"/>
@@ -9999,7 +10033,7 @@
         <v>23</v>
       </c>
       <c r="C669" s="16" t="s">
-        <v>534</v>
+        <v>520</v>
       </c>
       <c r="D669" s="16"/>
       <c r="E669" s="16"/>
@@ -10009,7 +10043,7 @@
         <v>2</v>
       </c>
       <c r="B670" s="18" t="s">
-        <v>535</v>
+        <v>521</v>
       </c>
       <c r="C670" s="16"/>
       <c r="D670" s="16"/>
@@ -10020,8 +10054,8 @@
       <c r="B671" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C671" s="64" t="s">
-        <v>536</v>
+      <c r="C671" s="62" t="s">
+        <v>522</v>
       </c>
       <c r="D671" s="16"/>
       <c r="E671" s="16"/>
@@ -10031,7 +10065,7 @@
         <v>3</v>
       </c>
       <c r="B672" s="2" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
     </row>
     <row r="673" spans="1:9">
@@ -10039,7 +10073,7 @@
         <v>23</v>
       </c>
       <c r="C673" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="674" spans="1:9">
@@ -10047,7 +10081,7 @@
         <v>5</v>
       </c>
       <c r="B674" s="2" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
     </row>
     <row r="675" spans="1:9">
@@ -10055,7 +10089,7 @@
         <v>23</v>
       </c>
       <c r="C675" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="676" spans="1:9">
@@ -10063,22 +10097,22 @@
         <v>6</v>
       </c>
       <c r="B676" s="2" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="677" spans="1:9">
       <c r="C677" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="678" spans="1:9">
       <c r="C678" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="679" spans="1:9">
       <c r="C679" s="2" t="s">
-        <v>506</v>
+        <v>492</v>
       </c>
     </row>
     <row r="680" spans="1:9">
@@ -10086,7 +10120,7 @@
         <v>7</v>
       </c>
       <c r="B680" s="2" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="681" spans="1:9">
@@ -10094,7 +10128,7 @@
         <v>23</v>
       </c>
       <c r="C681" s="2" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="682" spans="1:9">
@@ -10137,7 +10171,7 @@
     </row>
     <row r="686" spans="1:9">
       <c r="A686" s="12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B686" s="13"/>
       <c r="C686" s="13"/>
@@ -10160,7 +10194,7 @@
     <row r="688" spans="1:9">
       <c r="A688" s="15"/>
       <c r="B688" s="15" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C688" s="15"/>
       <c r="D688" s="15"/>
@@ -10196,7 +10230,7 @@
         <v>1</v>
       </c>
       <c r="B692" s="16" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C692" s="16"/>
       <c r="D692" s="16"/>
@@ -10207,7 +10241,7 @@
         <v>23</v>
       </c>
       <c r="C693" s="2" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="694" spans="1:9">
@@ -10281,7 +10315,7 @@
         <v>2</v>
       </c>
       <c r="B700" s="16" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C700" s="16"/>
       <c r="D700" s="25"/>
@@ -10297,7 +10331,7 @@
         <v>23</v>
       </c>
       <c r="C701" s="16" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D701" s="25"/>
       <c r="E701" s="25"/>
@@ -10388,7 +10422,7 @@
         <v>3</v>
       </c>
       <c r="B709" s="16" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C709" s="24"/>
       <c r="D709" s="25"/>
@@ -10404,7 +10438,7 @@
         <v>23</v>
       </c>
       <c r="C710" s="25" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D710" s="25"/>
       <c r="E710" s="25"/>
@@ -10594,7 +10628,7 @@
         <v>4</v>
       </c>
       <c r="B727" s="25" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C727" s="24"/>
       <c r="D727" s="25"/>
@@ -10610,7 +10644,7 @@
         <v>23</v>
       </c>
       <c r="C728" s="25" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D728" s="25"/>
       <c r="E728" s="25"/>
@@ -10786,7 +10820,7 @@
     </row>
     <row r="744" spans="1:9">
       <c r="A744" s="12" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B744" s="13"/>
       <c r="C744" s="13"/>
@@ -10809,7 +10843,7 @@
     <row r="746" spans="1:9">
       <c r="A746" s="15"/>
       <c r="B746" s="15" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C746" s="15"/>
       <c r="D746" s="15"/>
@@ -10845,7 +10879,7 @@
         <v>1</v>
       </c>
       <c r="B750" s="16" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C750" s="16"/>
       <c r="D750" s="16"/>
@@ -10856,7 +10890,7 @@
         <v>2</v>
       </c>
       <c r="B751" s="25" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C751" s="25"/>
       <c r="D751" s="25"/>
@@ -10872,7 +10906,7 @@
         <v>23</v>
       </c>
       <c r="C752" s="25" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D752" s="25"/>
       <c r="E752" s="25"/>
@@ -10886,7 +10920,7 @@
         <v>3</v>
       </c>
       <c r="B753" s="25" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C753" s="25"/>
       <c r="D753" s="25"/>
@@ -10902,7 +10936,7 @@
         <v>23</v>
       </c>
       <c r="C754" s="25" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D754" s="25"/>
       <c r="E754" s="25"/>
@@ -10916,7 +10950,7 @@
         <v>4</v>
       </c>
       <c r="B755" s="25" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C755" s="25"/>
       <c r="D755" s="25"/>
@@ -10932,7 +10966,7 @@
         <v>23</v>
       </c>
       <c r="C756" s="25" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D756" s="25"/>
       <c r="E756" s="25"/>
@@ -10946,7 +10980,7 @@
         <v>5</v>
       </c>
       <c r="B757" s="25" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C757" s="25"/>
       <c r="D757" s="25"/>
@@ -10962,7 +10996,7 @@
         <v>23</v>
       </c>
       <c r="C758" s="25" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D758" s="25"/>
       <c r="E758" s="25"/>
@@ -11050,7 +11084,7 @@
     </row>
     <row r="766" spans="1:9">
       <c r="A766" s="12" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B766" s="13"/>
       <c r="C766" s="13"/>
@@ -11073,7 +11107,7 @@
     <row r="768" spans="1:9">
       <c r="A768" s="15"/>
       <c r="B768" s="15" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C768" s="15"/>
       <c r="D768" s="15"/>
@@ -11109,7 +11143,7 @@
         <v>1</v>
       </c>
       <c r="B772" s="16" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C772" s="16"/>
       <c r="D772" s="16"/>
@@ -11120,7 +11154,7 @@
         <v>23</v>
       </c>
       <c r="C773" s="25" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D773" s="25"/>
       <c r="E773" s="25"/>
@@ -11184,7 +11218,7 @@
         <v>2</v>
       </c>
       <c r="B779" s="25" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C779" s="25"/>
       <c r="D779" s="25"/>
@@ -11200,7 +11234,7 @@
         <v>23</v>
       </c>
       <c r="C780" s="25" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D780" s="25"/>
       <c r="E780" s="25"/>
@@ -11288,7 +11322,7 @@
     </row>
     <row r="788" spans="1:9">
       <c r="A788" s="12" t="s">
-        <v>232</v>
+        <v>549</v>
       </c>
       <c r="B788" s="13"/>
       <c r="C788" s="13"/>
@@ -11311,7 +11345,7 @@
     <row r="790" spans="1:9">
       <c r="A790" s="15"/>
       <c r="B790" s="15" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C790" s="15"/>
       <c r="D790" s="15"/>
@@ -11329,7 +11363,7 @@
     <row r="792" spans="1:9">
       <c r="A792" s="14"/>
       <c r="B792" s="17" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C792" s="17"/>
       <c r="D792" s="15"/>
@@ -11349,7 +11383,7 @@
         <v>1</v>
       </c>
       <c r="B794" s="16" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="C794" s="16"/>
       <c r="D794" s="16"/>
@@ -11360,7 +11394,7 @@
         <v>2</v>
       </c>
       <c r="B795" s="25" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C795" s="25"/>
       <c r="D795" s="25"/>
@@ -11376,7 +11410,7 @@
         <v>23</v>
       </c>
       <c r="C796" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D796" s="25"/>
       <c r="E796" s="25"/>
@@ -11390,7 +11424,7 @@
         <v>3</v>
       </c>
       <c r="B797" s="15" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="C797" s="25"/>
       <c r="D797" s="25"/>
@@ -11405,7 +11439,7 @@
         <v>4</v>
       </c>
       <c r="B798" s="25" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C798" s="25"/>
       <c r="D798" s="25"/>
@@ -11421,7 +11455,7 @@
         <v>23</v>
       </c>
       <c r="C799" s="25" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D799" s="25"/>
       <c r="E799" s="25"/>
@@ -11434,7 +11468,7 @@
       <c r="A800" s="25"/>
       <c r="B800" s="25"/>
       <c r="C800" s="25" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D800" s="25"/>
       <c r="E800" s="25"/>
@@ -11448,7 +11482,7 @@
         <v>5</v>
       </c>
       <c r="B801" s="25" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C801" s="25"/>
       <c r="D801" s="25"/>
@@ -11464,7 +11498,7 @@
         <v>23</v>
       </c>
       <c r="C802" s="25" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D802" s="25"/>
       <c r="E802" s="25"/>
@@ -11618,7 +11652,7 @@
     </row>
     <row r="816" spans="1:9">
       <c r="A816" s="12" t="s">
-        <v>494</v>
+        <v>480</v>
       </c>
       <c r="B816" s="13"/>
       <c r="C816" s="13"/>
@@ -11627,7 +11661,7 @@
       <c r="F816" s="13"/>
       <c r="G816" s="13"/>
       <c r="H816" s="13" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="I816" s="13"/>
     </row>
@@ -11643,7 +11677,7 @@
     <row r="818" spans="1:9">
       <c r="A818" s="15"/>
       <c r="B818" s="15" t="s">
-        <v>495</v>
+        <v>481</v>
       </c>
       <c r="C818" s="15"/>
       <c r="D818" s="15"/>
@@ -11661,7 +11695,7 @@
     <row r="820" spans="1:9">
       <c r="A820" s="14"/>
       <c r="B820" s="17" t="s">
-        <v>496</v>
+        <v>482</v>
       </c>
       <c r="C820" s="17"/>
       <c r="D820" s="15"/>
@@ -11685,7 +11719,7 @@
         <v>1</v>
       </c>
       <c r="B822" s="16" t="s">
-        <v>497</v>
+        <v>483</v>
       </c>
       <c r="C822" s="16"/>
       <c r="D822" s="16"/>
@@ -11700,7 +11734,7 @@
         <v>2</v>
       </c>
       <c r="B823" s="25" t="s">
-        <v>498</v>
+        <v>484</v>
       </c>
       <c r="C823" s="25"/>
       <c r="D823" s="25"/>
@@ -11716,7 +11750,7 @@
         <v>23</v>
       </c>
       <c r="C824" s="25" t="s">
-        <v>499</v>
+        <v>485</v>
       </c>
       <c r="D824" s="25"/>
       <c r="E824" s="25"/>
@@ -11730,7 +11764,7 @@
         <v>3</v>
       </c>
       <c r="B825" s="25" t="s">
-        <v>500</v>
+        <v>486</v>
       </c>
       <c r="C825" s="24"/>
       <c r="D825" s="25"/>
@@ -11745,7 +11779,7 @@
         <v>4</v>
       </c>
       <c r="B826" s="25" t="s">
-        <v>501</v>
+        <v>487</v>
       </c>
       <c r="C826" s="24"/>
       <c r="D826" s="25"/>
@@ -11761,7 +11795,7 @@
         <v>23</v>
       </c>
       <c r="C827" s="25" t="s">
-        <v>502</v>
+        <v>488</v>
       </c>
       <c r="D827" s="25"/>
       <c r="E827" s="25"/>
@@ -11775,7 +11809,7 @@
         <v>5</v>
       </c>
       <c r="B828" s="25" t="s">
-        <v>503</v>
+        <v>489</v>
       </c>
       <c r="C828" s="24"/>
       <c r="D828" s="25"/>
@@ -11791,7 +11825,7 @@
         <v>23</v>
       </c>
       <c r="C829" s="25" t="s">
-        <v>504</v>
+        <v>490</v>
       </c>
       <c r="D829" s="25"/>
       <c r="E829" s="25"/>
@@ -11859,7 +11893,7 @@
     </row>
     <row r="835" spans="1:9">
       <c r="A835" s="12" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B835" s="13"/>
       <c r="C835" s="13"/>
@@ -11882,7 +11916,7 @@
     <row r="837" spans="1:9">
       <c r="A837" s="15"/>
       <c r="B837" s="15" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C837" s="15"/>
       <c r="D837" s="15"/>
@@ -11918,7 +11952,7 @@
         <v>1</v>
       </c>
       <c r="B841" s="16" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C841" s="16"/>
       <c r="D841" s="16"/>
@@ -11929,7 +11963,7 @@
         <v>2</v>
       </c>
       <c r="B842" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="843" spans="1:9">
@@ -11937,7 +11971,7 @@
         <v>23</v>
       </c>
       <c r="C843" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
     </row>
     <row r="844" spans="1:9">
@@ -11945,7 +11979,7 @@
         <v>3</v>
       </c>
       <c r="B844" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="845" spans="1:9">
@@ -11953,7 +11987,7 @@
         <v>23</v>
       </c>
       <c r="C845" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
     </row>
     <row r="846" spans="1:9">
@@ -11988,7 +12022,7 @@
         <v>4</v>
       </c>
       <c r="B855" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
     </row>
     <row r="856" spans="1:3">
@@ -11996,13 +12030,13 @@
         <v>23</v>
       </c>
       <c r="C856" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
     </row>
     <row r="857" spans="1:3">
       <c r="B857" s="18"/>
       <c r="C857" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
     </row>
     <row r="858" spans="1:3">
@@ -12028,7 +12062,7 @@
         <v>5</v>
       </c>
       <c r="B864" s="2" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
     </row>
     <row r="865" spans="2:3">
@@ -12036,12 +12070,12 @@
         <v>23</v>
       </c>
       <c r="C865" s="2" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
     </row>
     <row r="883" spans="1:11">
       <c r="A883" s="12" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B883" s="13"/>
       <c r="C883" s="13"/>
@@ -12064,7 +12098,7 @@
     <row r="885" spans="1:11">
       <c r="A885" s="15"/>
       <c r="B885" s="15" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C885" s="15"/>
       <c r="D885" s="15"/>
@@ -12100,7 +12134,7 @@
         <v>1</v>
       </c>
       <c r="B889" s="16" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C889" s="16"/>
       <c r="D889" s="16"/>
@@ -12111,7 +12145,7 @@
         <v>2</v>
       </c>
       <c r="B890" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
     </row>
     <row r="891" spans="1:11">
@@ -12119,12 +12153,12 @@
         <v>23</v>
       </c>
       <c r="C891" s="2" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
     </row>
     <row r="892" spans="1:11">
       <c r="K892" s="2" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
     </row>
     <row r="895" spans="1:11">
@@ -12132,7 +12166,7 @@
         <v>3</v>
       </c>
       <c r="B895" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="896" spans="1:11">
@@ -12140,12 +12174,12 @@
         <v>23</v>
       </c>
       <c r="C896" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
     </row>
     <row r="917" spans="1:9">
       <c r="A917" s="12" t="s">
-        <v>470</v>
+        <v>550</v>
       </c>
       <c r="B917" s="13"/>
       <c r="C917" s="13"/>
@@ -12168,7 +12202,7 @@
     <row r="919" spans="1:9">
       <c r="A919" s="15"/>
       <c r="B919" s="15" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C919" s="15"/>
       <c r="D919" s="15"/>
@@ -12204,7 +12238,7 @@
         <v>1</v>
       </c>
       <c r="B923" s="16" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C923" s="16"/>
       <c r="D923" s="16"/>
@@ -12215,7 +12249,7 @@
         <v>2</v>
       </c>
       <c r="B924" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
     </row>
     <row r="925" spans="1:9">
@@ -12223,7 +12257,7 @@
         <v>23</v>
       </c>
       <c r="C925" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
     </row>
     <row r="926" spans="1:9">
@@ -12231,7 +12265,7 @@
         <v>3</v>
       </c>
       <c r="B926" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
     </row>
     <row r="927" spans="1:9">
@@ -12239,7 +12273,7 @@
         <v>23</v>
       </c>
       <c r="C927" s="2" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
     </row>
     <row r="928" spans="1:9">
@@ -12247,7 +12281,7 @@
         <v>4</v>
       </c>
       <c r="B928" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="929" spans="1:3">
@@ -12255,7 +12289,7 @@
         <v>23</v>
       </c>
       <c r="C929" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
     </row>
     <row r="942" spans="1:3">
@@ -12263,7 +12297,7 @@
         <v>5</v>
       </c>
       <c r="B942" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
     </row>
     <row r="943" spans="1:3">
@@ -12271,12 +12305,12 @@
         <v>23</v>
       </c>
       <c r="C943" s="2" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
     </row>
     <row r="944" spans="1:3">
       <c r="C944" s="2" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
     </row>
     <row r="945" spans="1:3">
@@ -12284,7 +12318,7 @@
         <v>6</v>
       </c>
       <c r="B945" s="2" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
     </row>
     <row r="946" spans="1:3">
@@ -12292,7 +12326,7 @@
         <v>23</v>
       </c>
       <c r="C946" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
     </row>
     <row r="947" spans="1:3">
@@ -12300,7 +12334,7 @@
         <v>7</v>
       </c>
       <c r="B947" s="15" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
     </row>
     <row r="948" spans="1:3">
@@ -12308,22 +12342,22 @@
         <v>23</v>
       </c>
       <c r="C948" s="2" t="s">
-        <v>544</v>
+        <v>530</v>
       </c>
     </row>
     <row r="949" spans="1:3">
       <c r="C949" s="2" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
     </row>
     <row r="950" spans="1:3">
       <c r="C950" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="973" spans="1:9">
       <c r="A973" s="12" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B973" s="13"/>
       <c r="C973" s="13"/>
@@ -12346,7 +12380,7 @@
     <row r="975" spans="1:9">
       <c r="A975" s="15"/>
       <c r="B975" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C975" s="15"/>
       <c r="D975" s="15"/>
@@ -12382,7 +12416,7 @@
         <v>1</v>
       </c>
       <c r="B979" s="16" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C979" s="16"/>
       <c r="D979" s="16"/>
@@ -12393,7 +12427,7 @@
         <v>2</v>
       </c>
       <c r="B980" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="981" spans="1:9">
@@ -12401,7 +12435,7 @@
         <v>23</v>
       </c>
       <c r="C981" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="982" spans="1:9">
@@ -12409,7 +12443,7 @@
         <v>3</v>
       </c>
       <c r="B982" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="983" spans="1:9">
@@ -12417,48 +12451,48 @@
         <v>4</v>
       </c>
       <c r="B983" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
     </row>
     <row r="984" spans="1:9">
-      <c r="B984" s="65" t="s">
+      <c r="B984" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="C984" s="66" t="s">
-        <v>276</v>
-      </c>
-      <c r="D984" s="66"/>
-      <c r="E984" s="66"/>
-      <c r="F984" s="66"/>
+      <c r="C984" s="64" t="s">
+        <v>272</v>
+      </c>
+      <c r="D984" s="64"/>
+      <c r="E984" s="64"/>
+      <c r="F984" s="64"/>
       <c r="H984" s="2" t="s">
-        <v>538</v>
+        <v>524</v>
       </c>
     </row>
     <row r="985" spans="1:9" ht="16.5">
       <c r="A985" s="2">
         <v>5</v>
       </c>
-      <c r="B985" s="66" t="s">
-        <v>277</v>
-      </c>
-      <c r="C985" s="66"/>
-      <c r="D985" s="66"/>
-      <c r="E985" s="66"/>
-      <c r="F985" s="66"/>
+      <c r="B985" s="64" t="s">
+        <v>273</v>
+      </c>
+      <c r="C985" s="64"/>
+      <c r="D985" s="64"/>
+      <c r="E985" s="64"/>
+      <c r="F985" s="64"/>
       <c r="H985" s="2" t="s">
-        <v>537</v>
+        <v>523</v>
       </c>
     </row>
     <row r="986" spans="1:9">
-      <c r="B986" s="65" t="s">
+      <c r="B986" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="C986" s="66" t="s">
-        <v>278</v>
-      </c>
-      <c r="D986" s="66"/>
-      <c r="E986" s="66"/>
-      <c r="F986" s="66"/>
+      <c r="C986" s="64" t="s">
+        <v>274</v>
+      </c>
+      <c r="D986" s="64"/>
+      <c r="E986" s="64"/>
+      <c r="F986" s="64"/>
     </row>
     <row r="988" spans="1:9" ht="7.5" customHeight="1">
       <c r="A988" s="23"/>
@@ -12486,7 +12520,7 @@
     </row>
     <row r="991" spans="1:9">
       <c r="A991" s="12" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B991" s="13"/>
       <c r="C991" s="13"/>
@@ -12509,7 +12543,7 @@
     <row r="993" spans="1:5">
       <c r="A993" s="15"/>
       <c r="B993" s="15" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C993" s="15"/>
       <c r="D993" s="15"/>
@@ -12545,7 +12579,7 @@
         <v>1</v>
       </c>
       <c r="B997" s="16" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C997" s="16"/>
       <c r="D997" s="16"/>
@@ -12556,12 +12590,12 @@
         <v>23</v>
       </c>
       <c r="C998" s="2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="999" spans="1:5">
       <c r="C999" s="2" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="1000" spans="1:5">
@@ -12569,7 +12603,7 @@
         <v>2</v>
       </c>
       <c r="B1000" s="2" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="1001" spans="1:5">
@@ -12577,7 +12611,7 @@
         <v>23</v>
       </c>
       <c r="C1001" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -12620,7 +12654,7 @@
     <row r="4" spans="1:9">
       <c r="A4" s="2"/>
       <c r="B4" s="7" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -12630,7 +12664,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="B5" s="7" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -12640,7 +12674,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="B6" s="7" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -12687,7 +12721,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="11" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -12711,7 +12745,7 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="12" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -12738,7 +12772,7 @@
     <row r="15" spans="1:9">
       <c r="A15" s="15"/>
       <c r="B15" s="15" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -12790,7 +12824,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
@@ -12806,7 +12840,7 @@
         <v>23</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="D20" s="16"/>
       <c r="E20" s="16"/>
@@ -12963,7 +12997,7 @@
         <v>2</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
@@ -13140,7 +13174,7 @@
     </row>
     <row r="50" spans="1:9">
       <c r="A50" s="12" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
@@ -13167,7 +13201,7 @@
     <row r="52" spans="1:9">
       <c r="A52" s="15"/>
       <c r="B52" s="15" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C52" s="15"/>
       <c r="D52" s="15"/>
@@ -13219,7 +13253,7 @@
         <v>1</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C56" s="16"/>
       <c r="D56" s="16"/>
@@ -13235,7 +13269,7 @@
         <v>23</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="D57" s="2"/>
       <c r="E57" s="2"/>
@@ -13249,7 +13283,7 @@
         <v>2</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -13265,7 +13299,7 @@
         <v>23</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D59" s="2"/>
       <c r="E59" s="2"/>
@@ -13279,7 +13313,7 @@
         <v>3</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -13295,7 +13329,7 @@
         <v>23</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="D61" s="2"/>
       <c r="E61" s="2"/>
@@ -13328,7 +13362,7 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="12" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B64" s="13"/>
       <c r="C64" s="13"/>
@@ -13355,7 +13389,7 @@
     <row r="66" spans="1:9">
       <c r="A66" s="15"/>
       <c r="B66" s="15" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C66" s="15"/>
       <c r="D66" s="15"/>
@@ -13407,7 +13441,7 @@
         <v>1</v>
       </c>
       <c r="B70" s="16" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C70" s="16"/>
       <c r="D70" s="16"/>
@@ -13422,7 +13456,7 @@
         <v>2</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -13436,7 +13470,7 @@
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2" t="s">
-        <v>507</v>
+        <v>493</v>
       </c>
       <c r="D72" s="2"/>
       <c r="E72" s="2"/>
@@ -13449,7 +13483,7 @@
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
       <c r="C73" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D73" s="2"/>
       <c r="E73" s="2"/>
@@ -13462,7 +13496,7 @@
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="C74" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
@@ -13475,7 +13509,7 @@
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
       <c r="C75" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
@@ -13489,7 +13523,7 @@
         <v>3</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
@@ -13505,7 +13539,7 @@
         <v>23</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="D77" s="2"/>
       <c r="E77" s="2"/>
@@ -13518,7 +13552,7 @@
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="C78" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D78" s="2"/>
       <c r="E78" s="2"/>
@@ -13531,7 +13565,7 @@
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
@@ -13544,7 +13578,7 @@
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
@@ -13557,7 +13591,7 @@
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D81" s="2"/>
       <c r="E81" s="2"/>
@@ -13579,7 +13613,7 @@
     </row>
     <row r="83" spans="1:9">
       <c r="A83" s="12" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B83" s="13"/>
       <c r="C83" s="13"/>
@@ -13606,7 +13640,7 @@
     <row r="85" spans="1:9">
       <c r="A85" s="15"/>
       <c r="B85" s="15" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C85" s="15"/>
       <c r="D85" s="15"/>
@@ -13658,7 +13692,7 @@
         <v>1</v>
       </c>
       <c r="B89" s="16" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C89" s="16"/>
       <c r="D89" s="16"/>
@@ -13673,7 +13707,7 @@
         <v>2</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
@@ -13689,7 +13723,7 @@
         <v>23</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" s="2"/>
@@ -13702,7 +13736,7 @@
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" s="2"/>
@@ -13836,7 +13870,7 @@
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="19" t="s">
-        <v>489</v>
+        <v>475</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" s="2"/>
@@ -13850,7 +13884,7 @@
         <v>3</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
@@ -13858,8 +13892,8 @@
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
       <c r="H105" s="2"/>
-      <c r="I105" s="44" t="s">
-        <v>491</v>
+      <c r="I105" s="42" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -13867,7 +13901,7 @@
         <v>4</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>488</v>
+        <v>474</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
@@ -13883,7 +13917,7 @@
         <v>23</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" s="2"/>
@@ -13896,7 +13930,7 @@
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" s="2"/>
@@ -14039,7 +14073,7 @@
     </row>
     <row r="121" spans="1:9">
       <c r="A121" s="12" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B121" s="13"/>
       <c r="C121" s="13"/>
@@ -14066,7 +14100,7 @@
     <row r="123" spans="1:9">
       <c r="A123" s="15"/>
       <c r="B123" s="15" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C123" s="15"/>
       <c r="D123" s="15"/>
@@ -14118,7 +14152,7 @@
         <v>1</v>
       </c>
       <c r="B127" s="16" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C127" s="16"/>
       <c r="D127" s="16"/>
@@ -14133,7 +14167,7 @@
         <v>2</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" s="2"/>
@@ -14149,7 +14183,7 @@
         <v>23</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" s="2"/>
@@ -14163,7 +14197,7 @@
         <v>3</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
@@ -14179,7 +14213,7 @@
         <v>23</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" s="2"/>
@@ -14212,7 +14246,7 @@
     </row>
     <row r="135" spans="1:9">
       <c r="A135" s="11" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -14236,7 +14270,7 @@
     </row>
     <row r="137" spans="1:9">
       <c r="A137" s="12" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B137" s="13"/>
       <c r="C137" s="13"/>
@@ -14263,7 +14297,7 @@
     <row r="139" spans="1:9">
       <c r="A139" s="15"/>
       <c r="B139" s="15" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C139" s="15"/>
       <c r="D139" s="15"/>
@@ -14289,7 +14323,7 @@
     <row r="141" spans="1:9">
       <c r="A141" s="14"/>
       <c r="B141" s="17" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C141" s="17"/>
       <c r="D141" s="15"/>
@@ -14317,7 +14351,7 @@
         <v>1</v>
       </c>
       <c r="B143" s="16" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C143" s="16"/>
       <c r="D143" s="16"/>
@@ -14333,7 +14367,7 @@
         <v>23</v>
       </c>
       <c r="C144" s="16" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D144" s="16"/>
       <c r="E144" s="16"/>
@@ -14347,7 +14381,7 @@
         <v>2</v>
       </c>
       <c r="B145" s="1" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="146" spans="1:9">
@@ -14355,7 +14389,7 @@
         <v>23</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="147" spans="1:9">
@@ -14363,7 +14397,7 @@
         <v>3</v>
       </c>
       <c r="B147" s="1" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="148" spans="1:9">
@@ -14371,7 +14405,7 @@
         <v>23</v>
       </c>
       <c r="C148" s="16" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="149" spans="1:9">
@@ -14379,7 +14413,7 @@
         <v>4</v>
       </c>
       <c r="B149" s="1" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="150" spans="1:9">
@@ -14387,12 +14421,12 @@
         <v>23</v>
       </c>
       <c r="C150" s="16" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="152" spans="1:9">
       <c r="A152" s="12" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B152" s="13"/>
       <c r="C152" s="13"/>
@@ -14419,7 +14453,7 @@
     <row r="154" spans="1:9">
       <c r="A154" s="15"/>
       <c r="B154" s="15" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C154" s="15"/>
       <c r="D154" s="15"/>
@@ -14471,7 +14505,7 @@
         <v>1</v>
       </c>
       <c r="B158" s="16" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C158" s="16"/>
       <c r="D158" s="16"/>
@@ -14487,7 +14521,7 @@
         <v>23</v>
       </c>
       <c r="C159" s="16" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D159" s="16"/>
       <c r="E159" s="16"/>
@@ -14501,7 +14535,7 @@
         <v>2</v>
       </c>
       <c r="B174" s="1" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="175" spans="1:3">
@@ -14509,12 +14543,12 @@
         <v>23</v>
       </c>
       <c r="C175" s="16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="187" spans="1:9">
       <c r="A187" s="12" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B187" s="13"/>
       <c r="C187" s="13"/>
@@ -14541,7 +14575,7 @@
     <row r="189" spans="1:9">
       <c r="A189" s="15"/>
       <c r="B189" s="15" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C189" s="15"/>
       <c r="D189" s="15"/>
@@ -14593,7 +14627,7 @@
         <v>1</v>
       </c>
       <c r="B193" s="16" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C193" s="16"/>
       <c r="D193" s="16"/>
@@ -14608,7 +14642,7 @@
         <v>2</v>
       </c>
       <c r="B194" s="1" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D194" s="16"/>
       <c r="E194" s="16"/>
@@ -14622,7 +14656,7 @@
         <v>23</v>
       </c>
       <c r="C195" s="16" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
     </row>
     <row r="196" spans="1:9">
@@ -14630,7 +14664,7 @@
         <v>3</v>
       </c>
       <c r="B196" s="1" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="197" spans="1:9">
@@ -14638,7 +14672,7 @@
         <v>23</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
     </row>
     <row r="198" spans="1:9">
@@ -14646,7 +14680,7 @@
         <v>4</v>
       </c>
       <c r="B198" s="1" t="s">
-        <v>508</v>
+        <v>494</v>
       </c>
     </row>
     <row r="199" spans="1:9">
@@ -14654,7 +14688,7 @@
         <v>23</v>
       </c>
       <c r="C199" s="1" t="s">
-        <v>509</v>
+        <v>495</v>
       </c>
     </row>
     <row r="200" spans="1:9">
@@ -14662,7 +14696,7 @@
     </row>
     <row r="201" spans="1:9">
       <c r="A201" s="12" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B201" s="13"/>
       <c r="C201" s="13"/>
@@ -14689,7 +14723,7 @@
     <row r="203" spans="1:9">
       <c r="A203" s="15"/>
       <c r="B203" s="15" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C203" s="15"/>
       <c r="D203" s="15"/>
@@ -14741,7 +14775,7 @@
         <v>1</v>
       </c>
       <c r="B207" s="16" t="s">
-        <v>492</v>
+        <v>478</v>
       </c>
       <c r="C207" s="16"/>
       <c r="D207" s="16"/>
@@ -14756,13 +14790,13 @@
         <v>23</v>
       </c>
       <c r="C208" s="1" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
     </row>
     <row r="209" spans="1:3">
       <c r="B209" s="18"/>
       <c r="C209" s="1" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
     </row>
     <row r="210" spans="1:3">
@@ -14770,7 +14804,7 @@
         <v>2</v>
       </c>
       <c r="B210" s="15" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="211" spans="1:3">
@@ -14778,7 +14812,7 @@
         <v>23</v>
       </c>
       <c r="C211" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="212" spans="1:3">
@@ -14807,7 +14841,7 @@
         <v>3</v>
       </c>
       <c r="B219" s="15" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
     </row>
     <row r="220" spans="1:3">
@@ -14815,7 +14849,7 @@
         <v>23</v>
       </c>
       <c r="C220" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="221" spans="1:3">
@@ -14841,7 +14875,7 @@
     </row>
     <row r="229" spans="1:9">
       <c r="A229" s="12" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B229" s="13"/>
       <c r="C229" s="13"/>
@@ -14868,7 +14902,7 @@
     <row r="231" spans="1:9">
       <c r="A231" s="15"/>
       <c r="B231" s="15" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C231" s="15"/>
       <c r="D231" s="15"/>
@@ -14920,7 +14954,7 @@
         <v>1</v>
       </c>
       <c r="B235" s="16" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C235" s="16"/>
       <c r="D235" s="16"/>
@@ -14935,12 +14969,12 @@
         <v>23</v>
       </c>
       <c r="C236" s="1" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="237" spans="1:9">
       <c r="C237" s="1" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="251" spans="1:3">
@@ -14948,7 +14982,7 @@
         <v>2</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
     </row>
     <row r="252" spans="1:3">
@@ -14956,7 +14990,7 @@
         <v>23</v>
       </c>
       <c r="C252" s="1" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="255" spans="1:3">
@@ -14964,7 +14998,7 @@
         <v>3</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="256" spans="1:3">
@@ -14972,12 +15006,12 @@
         <v>23</v>
       </c>
       <c r="C256" s="1" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="260" spans="3:3">
       <c r="C260" s="1" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
     </row>
     <row r="274" spans="1:11">
@@ -14985,7 +15019,7 @@
         <v>3</v>
       </c>
       <c r="B274" s="1" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="275" spans="1:11">
@@ -14993,7 +15027,7 @@
         <v>23</v>
       </c>
       <c r="C275" s="1" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="276" spans="1:11">
@@ -15001,7 +15035,7 @@
     </row>
     <row r="277" spans="1:11">
       <c r="A277" s="12" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B277" s="13"/>
       <c r="C277" s="13"/>
@@ -15028,7 +15062,7 @@
     <row r="279" spans="1:11">
       <c r="A279" s="15"/>
       <c r="B279" s="15" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C279" s="15"/>
       <c r="D279" s="15"/>
@@ -15080,7 +15114,7 @@
         <v>1</v>
       </c>
       <c r="B283" s="16" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C283" s="16"/>
       <c r="D283" s="16"/>
@@ -15090,7 +15124,7 @@
       <c r="H283" s="16"/>
       <c r="I283" s="16"/>
       <c r="K283" s="1" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -15098,7 +15132,7 @@
         <v>2</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="285" spans="1:11">
@@ -15106,7 +15140,7 @@
         <v>23</v>
       </c>
       <c r="C285" s="1" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="286" spans="1:11">
@@ -15114,7 +15148,7 @@
         <v>3</v>
       </c>
       <c r="B286" s="15" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="287" spans="1:11">
@@ -15122,13 +15156,13 @@
         <v>23</v>
       </c>
       <c r="C287" s="1" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="288" spans="1:11">
       <c r="B288" s="18"/>
       <c r="C288" s="1" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="289" spans="2:2">
@@ -15199,7 +15233,7 @@
     </row>
     <row r="311" spans="1:9">
       <c r="A311" s="12" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B311" s="13"/>
       <c r="C311" s="13"/>
@@ -15226,7 +15260,7 @@
     <row r="313" spans="1:9">
       <c r="A313" s="15"/>
       <c r="B313" s="15" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C313" s="15"/>
       <c r="D313" s="15"/>
@@ -15278,7 +15312,7 @@
         <v>1</v>
       </c>
       <c r="B317" s="16" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C317" s="16"/>
       <c r="D317" s="16"/>
@@ -15293,7 +15327,7 @@
         <v>23</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="330" spans="1:3">
@@ -15301,7 +15335,7 @@
         <v>2</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="331" spans="1:3">
@@ -15309,7 +15343,7 @@
         <v>23</v>
       </c>
       <c r="C331" s="1" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="343" spans="1:5">
@@ -15317,7 +15351,7 @@
         <v>3</v>
       </c>
       <c r="B343" s="1" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="344" spans="1:5">
@@ -15325,7 +15359,7 @@
         <v>23</v>
       </c>
       <c r="C344" s="1" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
     </row>
     <row r="348" spans="1:5">
@@ -15333,7 +15367,7 @@
         <v>4</v>
       </c>
       <c r="B348" s="1" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="349" spans="1:5">
@@ -15341,60 +15375,60 @@
         <v>23</v>
       </c>
       <c r="C349" s="1" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="350" spans="1:5">
       <c r="C350" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="351" spans="1:5">
       <c r="C351" s="1" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="352" spans="1:5">
       <c r="C352" s="1" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="353" spans="1:9">
       <c r="C353" s="1" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="354" spans="1:9">
       <c r="C354" s="1" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
     </row>
     <row r="355" spans="1:9">
       <c r="C355" s="1" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
     </row>
     <row r="357" spans="1:9">
       <c r="A357" s="12" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B357" s="13"/>
       <c r="C357" s="13"/>
@@ -15421,7 +15455,7 @@
     <row r="359" spans="1:9">
       <c r="A359" s="15"/>
       <c r="B359" s="15" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C359" s="15"/>
       <c r="D359" s="15"/>
@@ -15473,7 +15507,7 @@
         <v>1</v>
       </c>
       <c r="B363" s="16" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C363" s="16"/>
       <c r="D363" s="16"/>
@@ -15489,7 +15523,7 @@
         <v>23</v>
       </c>
       <c r="C364" s="16" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D364" s="16"/>
       <c r="E364" s="16"/>
@@ -15502,7 +15536,7 @@
       <c r="A365" s="16"/>
       <c r="B365" s="16"/>
       <c r="C365" s="16" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D365" s="16"/>
       <c r="E365" s="16"/>
@@ -15667,7 +15701,7 @@
     </row>
     <row r="380" spans="1:9">
       <c r="A380" s="12" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B380" s="13"/>
       <c r="C380" s="13"/>
@@ -15694,7 +15728,7 @@
     <row r="382" spans="1:9">
       <c r="A382" s="15"/>
       <c r="B382" s="15" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C382" s="15"/>
       <c r="D382" s="15"/>
@@ -15746,7 +15780,7 @@
         <v>1</v>
       </c>
       <c r="B386" s="16" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C386" s="16"/>
       <c r="D386" s="16"/>
@@ -15761,7 +15795,7 @@
         <v>23</v>
       </c>
       <c r="C387" s="1" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="388" spans="1:9">
@@ -15769,7 +15803,7 @@
         <v>2</v>
       </c>
       <c r="B388" s="1" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="389" spans="1:9">
@@ -15777,12 +15811,12 @@
         <v>23</v>
       </c>
       <c r="C389" s="1" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="408" spans="1:9">
       <c r="A408" s="12" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B408" s="13"/>
       <c r="C408" s="13"/>
@@ -15809,7 +15843,7 @@
     <row r="410" spans="1:9">
       <c r="A410" s="15"/>
       <c r="B410" s="15" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C410" s="15"/>
       <c r="D410" s="15"/>
@@ -15861,7 +15895,7 @@
         <v>1</v>
       </c>
       <c r="B414" s="16" t="s">
-        <v>456</v>
+        <v>538</v>
       </c>
       <c r="C414" s="16"/>
       <c r="D414" s="16"/>
@@ -15876,7 +15910,7 @@
         <v>23</v>
       </c>
       <c r="C415" s="1" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="423" spans="1:9">
@@ -15884,7 +15918,7 @@
         <v>2</v>
       </c>
       <c r="B423" s="1" t="s">
-        <v>455</v>
+        <v>539</v>
       </c>
     </row>
     <row r="424" spans="1:9">
@@ -15892,7 +15926,7 @@
         <v>23</v>
       </c>
       <c r="C424" s="1" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="426" spans="1:9" ht="6" customHeight="1">
@@ -15908,12 +15942,12 @@
     </row>
     <row r="427" spans="1:9">
       <c r="A427" s="20" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
     </row>
     <row r="429" spans="1:9">
       <c r="A429" s="12" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B429" s="13"/>
       <c r="C429" s="13"/>
@@ -15940,7 +15974,7 @@
     <row r="431" spans="1:9">
       <c r="A431" s="15"/>
       <c r="B431" s="15" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C431" s="15"/>
       <c r="D431" s="15"/>
@@ -15992,7 +16026,7 @@
         <v>1</v>
       </c>
       <c r="B435" s="16" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C435" s="16"/>
       <c r="D435" s="16"/>
@@ -16007,7 +16041,7 @@
         <v>2</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="437" spans="1:9">
@@ -16015,7 +16049,7 @@
         <v>23</v>
       </c>
       <c r="C437" s="1" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="447" spans="1:9">
@@ -16023,7 +16057,7 @@
         <v>3</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="448" spans="1:9">
@@ -16031,17 +16065,17 @@
         <v>23</v>
       </c>
       <c r="C448" s="1" t="s">
-        <v>539</v>
+        <v>525</v>
       </c>
     </row>
     <row r="458" spans="1:3">
       <c r="C458" s="1" t="s">
-        <v>540</v>
+        <v>526</v>
       </c>
     </row>
     <row r="459" spans="1:3">
       <c r="C459" s="1" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
     </row>
     <row r="460" spans="1:3">
@@ -16049,7 +16083,7 @@
         <v>4</v>
       </c>
       <c r="B460" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="461" spans="1:3">
@@ -16057,7 +16091,7 @@
         <v>23</v>
       </c>
       <c r="C461" s="1" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="462" spans="1:3">
@@ -16065,7 +16099,7 @@
         <v>5</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="463" spans="1:3">
@@ -16073,12 +16107,12 @@
         <v>23</v>
       </c>
       <c r="C463" s="1" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="472" spans="1:9">
       <c r="A472" s="12" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B472" s="13"/>
       <c r="C472" s="13"/>
@@ -16105,7 +16139,7 @@
     <row r="474" spans="1:9">
       <c r="A474" s="15"/>
       <c r="B474" s="15" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="C474" s="15"/>
       <c r="D474" s="15"/>
@@ -16157,7 +16191,7 @@
         <v>1</v>
       </c>
       <c r="B478" s="16" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C478" s="16"/>
       <c r="D478" s="16"/>
@@ -16172,7 +16206,7 @@
         <v>23</v>
       </c>
       <c r="C479" s="1" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
     </row>
     <row r="480" spans="1:9">
@@ -16180,7 +16214,7 @@
         <v>2</v>
       </c>
       <c r="B480" s="1" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="481" spans="1:10">
@@ -16188,7 +16222,7 @@
         <v>23</v>
       </c>
       <c r="C481" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="485" spans="1:10">
@@ -16196,7 +16230,7 @@
         <v>3</v>
       </c>
       <c r="B485" s="1" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="486" spans="1:10">
@@ -16204,12 +16238,12 @@
         <v>23</v>
       </c>
       <c r="C486" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="487" spans="1:10">
       <c r="J487" s="1" t="s">
-        <v>543</v>
+        <v>529</v>
       </c>
     </row>
     <row r="490" spans="1:10">
@@ -16217,7 +16251,7 @@
         <v>4</v>
       </c>
       <c r="B490" s="1" t="s">
-        <v>542</v>
+        <v>528</v>
       </c>
     </row>
     <row r="491" spans="1:10">
@@ -16225,7 +16259,7 @@
         <v>23</v>
       </c>
       <c r="C491" s="1" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="495" spans="1:10">
@@ -16233,7 +16267,7 @@
         <v>5</v>
       </c>
       <c r="B495" s="1" t="s">
-        <v>493</v>
+        <v>479</v>
       </c>
     </row>
     <row r="496" spans="1:10">
@@ -16241,7 +16275,7 @@
         <v>23</v>
       </c>
       <c r="C496" s="1" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="497" spans="1:9">
@@ -16249,7 +16283,7 @@
     </row>
     <row r="509" spans="1:9">
       <c r="A509" s="12" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B509" s="13"/>
       <c r="C509" s="13"/>
@@ -16276,7 +16310,7 @@
     <row r="511" spans="1:9">
       <c r="A511" s="15"/>
       <c r="B511" s="15" t="s">
-        <v>422</v>
+        <v>540</v>
       </c>
       <c r="C511" s="15"/>
       <c r="D511" s="15"/>
@@ -16328,7 +16362,7 @@
         <v>1</v>
       </c>
       <c r="B515" s="16" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C515" s="16"/>
       <c r="D515" s="16"/>
@@ -16343,7 +16377,7 @@
         <v>2</v>
       </c>
       <c r="B516" s="1" t="s">
-        <v>424</v>
+        <v>541</v>
       </c>
     </row>
     <row r="517" spans="1:10">
@@ -16351,13 +16385,13 @@
         <v>23</v>
       </c>
       <c r="C517" s="1" t="s">
-        <v>425</v>
+        <v>542</v>
       </c>
       <c r="J517" s="21"/>
     </row>
     <row r="524" spans="1:10">
       <c r="A524" s="12" t="s">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="B524" s="13"/>
       <c r="C524" s="13"/>
@@ -16384,7 +16418,7 @@
     <row r="526" spans="1:10">
       <c r="A526" s="15"/>
       <c r="B526" s="15" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C526" s="15"/>
       <c r="D526" s="15"/>
@@ -16436,7 +16470,7 @@
         <v>1</v>
       </c>
       <c r="B530" s="16" t="s">
-        <v>428</v>
+        <v>421</v>
       </c>
       <c r="C530" s="16"/>
       <c r="D530" s="16"/>
@@ -16451,7 +16485,7 @@
         <v>2</v>
       </c>
       <c r="B531" s="1" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
     </row>
     <row r="537" spans="1:9">
@@ -16459,7 +16493,7 @@
         <v>3</v>
       </c>
       <c r="B537" s="1" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
     </row>
     <row r="538" spans="1:9">
@@ -16467,17 +16501,17 @@
         <v>23</v>
       </c>
       <c r="C538" s="1" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
     </row>
     <row r="545" spans="1:9">
       <c r="B545" s="1" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
     </row>
     <row r="547" spans="1:9">
       <c r="A547" s="12" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="B547" s="13"/>
       <c r="C547" s="13"/>
@@ -16504,7 +16538,7 @@
     <row r="549" spans="1:9">
       <c r="A549" s="15"/>
       <c r="B549" s="15" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="C549" s="15"/>
       <c r="D549" s="15"/>
@@ -16556,7 +16590,7 @@
         <v>1</v>
       </c>
       <c r="B553" s="16" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="C553" s="16"/>
       <c r="D553" s="16"/>
@@ -16571,7 +16605,7 @@
         <v>2</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="560" spans="1:9">
@@ -16579,7 +16613,7 @@
         <v>3</v>
       </c>
       <c r="B560" s="1" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="561" spans="1:9">
@@ -16587,17 +16621,17 @@
         <v>23</v>
       </c>
       <c r="C561" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="569" spans="1:9">
       <c r="B569" s="1" t="s">
-        <v>510</v>
+        <v>496</v>
       </c>
     </row>
     <row r="572" spans="1:9">
       <c r="A572" s="12" t="s">
-        <v>459</v>
+        <v>545</v>
       </c>
       <c r="B572" s="13"/>
       <c r="C572" s="13"/>
@@ -16624,7 +16658,7 @@
     <row r="574" spans="1:9">
       <c r="A574" s="15"/>
       <c r="B574" s="15" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="C574" s="15"/>
       <c r="D574" s="15"/>
@@ -16676,7 +16710,7 @@
         <v>1</v>
       </c>
       <c r="B578" s="16" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="C578" s="16"/>
       <c r="D578" s="16"/>
@@ -16691,15 +16725,15 @@
         <v>2</v>
       </c>
       <c r="B579" s="1" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
     </row>
     <row r="580" spans="1:9">
       <c r="B580" s="16" t="s">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="C580" s="16" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
       <c r="D580" s="16"/>
       <c r="E580" s="16"/>
@@ -16707,7 +16741,7 @@
     </row>
     <row r="581" spans="1:9">
       <c r="C581" s="16" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="D581" s="16"/>
       <c r="E581" s="16"/>
@@ -16715,7 +16749,7 @@
     </row>
     <row r="582" spans="1:9">
       <c r="C582" s="16" t="s">
-        <v>439</v>
+        <v>432</v>
       </c>
       <c r="D582" s="16"/>
       <c r="E582" s="16"/>
@@ -16723,7 +16757,7 @@
     </row>
     <row r="583" spans="1:9">
       <c r="C583" s="16" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="D583" s="16"/>
       <c r="E583" s="16"/>
@@ -16734,15 +16768,15 @@
         <v>3</v>
       </c>
       <c r="B584" s="1" t="s">
-        <v>443</v>
+        <v>544</v>
       </c>
     </row>
     <row r="585" spans="1:9">
       <c r="B585" s="18" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="C585" s="1" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
     </row>
     <row r="586" spans="1:9">
@@ -16750,7 +16784,7 @@
         <v>4</v>
       </c>
       <c r="B586" s="1" t="s">
-        <v>442</v>
+        <v>546</v>
       </c>
     </row>
     <row r="587" spans="1:9">
@@ -16758,7 +16792,7 @@
         <v>5</v>
       </c>
       <c r="B587" s="1" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
     </row>
     <row r="588" spans="1:9">
@@ -16766,7 +16800,7 @@
         <v>23</v>
       </c>
       <c r="C588" s="1" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
     </row>
     <row r="589" spans="1:9">
@@ -16774,7 +16808,7 @@
         <v>6</v>
       </c>
       <c r="B589" s="1" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
     </row>
     <row r="590" spans="1:9">
@@ -16782,7 +16816,7 @@
         <v>7</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="591" spans="1:9">
@@ -16790,7 +16824,7 @@
         <v>8</v>
       </c>
       <c r="B591" s="1" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
     </row>
     <row r="592" spans="1:9">
@@ -16798,7 +16832,7 @@
         <v>9</v>
       </c>
       <c r="B592" s="1" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
     </row>
     <row r="605" spans="2:3">
@@ -16806,17 +16840,17 @@
         <v>23</v>
       </c>
       <c r="C605" s="1" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
     </row>
     <row r="615" spans="1:9">
       <c r="B615" s="1" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
     </row>
     <row r="617" spans="1:9">
       <c r="A617" s="12" t="s">
-        <v>471</v>
+        <v>458</v>
       </c>
       <c r="B617" s="13"/>
       <c r="C617" s="13"/>
@@ -16843,7 +16877,7 @@
     <row r="619" spans="1:9">
       <c r="A619" s="15"/>
       <c r="B619" s="15" t="s">
-        <v>472</v>
+        <v>459</v>
       </c>
       <c r="C619" s="15"/>
       <c r="D619" s="15"/>
@@ -16895,7 +16929,7 @@
         <v>1</v>
       </c>
       <c r="B623" s="16" t="s">
-        <v>473</v>
+        <v>460</v>
       </c>
       <c r="C623" s="16"/>
       <c r="D623" s="16"/>
@@ -16910,15 +16944,15 @@
         <v>2</v>
       </c>
       <c r="B624" s="1" t="s">
-        <v>474</v>
+        <v>543</v>
       </c>
     </row>
     <row r="625" spans="2:4">
       <c r="B625" s="18" t="s">
-        <v>444</v>
+        <v>435</v>
       </c>
       <c r="C625" s="2" t="s">
-        <v>475</v>
+        <v>461</v>
       </c>
       <c r="D625" s="2"/>
     </row>

--- a/docs/vsscript/VSScript-Manual-Case.xlsx
+++ b/docs/vsscript/VSScript-Manual-Case.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\inetsoft\stylebi\test\datatest\docs\vsscript\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\inetsoft\stylebiold\test\datatest\docs\vsscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="OverView" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="552">
   <si>
     <t>Note:</t>
   </si>
@@ -2044,6 +2044,10 @@
   </si>
   <si>
     <t>TestCase-TextActions</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>In EM, add properties: javascript.java.packages=inetsoft.sree,inetsoft.web</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
 </sst>
@@ -16164,7 +16168,9 @@
     </row>
     <row r="476" spans="1:9">
       <c r="A476" s="14"/>
-      <c r="B476" s="17"/>
+      <c r="B476" s="17" t="s">
+        <v>551</v>
+      </c>
       <c r="C476" s="17"/>
       <c r="D476" s="15"/>
       <c r="E476" s="15"/>

--- a/docs/vsscript/VSScript-Manual-Case.xlsx
+++ b/docs/vsscript/VSScript-Manual-Case.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\inetsoft\stylebi\test\datatest\docs\vsscript\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\inetsoft\stylebiold\test\datatest\docs\vsscript\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="OverView" sheetId="3" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="916" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="917" uniqueCount="552">
   <si>
     <t>Note:</t>
   </si>
@@ -2045,6 +2045,9 @@
   <si>
     <t>TestCase-TextActions</t>
     <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>In EM, add properties: javascript.java.packages=inetsoft.sree,inetsoft.web</t>
   </si>
 </sst>
 </file>
@@ -16164,7 +16167,9 @@
     </row>
     <row r="476" spans="1:9">
       <c r="A476" s="14"/>
-      <c r="B476" s="17"/>
+      <c r="B476" s="17" t="s">
+        <v>551</v>
+      </c>
       <c r="C476" s="17"/>
       <c r="D476" s="15"/>
       <c r="E476" s="15"/>
